--- a/data/trans_orig/LAWTONBRODY_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY_2023-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,66</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,53</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,81</t>
+          <t>7,46; 7,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,53</t>
+          <t>6,86; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,66</t>
+          <t>7,34; 7,67</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,42</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,29</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,6</t>
+          <t>7,12; 7,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 7,4</t>
+          <t>6,51; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,48</t>
+          <t>7,02; 7,47</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,45</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,95</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,47</t>
+          <t>6,91; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 6,9</t>
+          <t>5,87; 6,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,21</t>
+          <t>6,68; 7,17</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>6,65</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 6,81</t>
+          <t>6,32; 6,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,91</t>
+          <t>6,46; 7,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,65</t>
+          <t>6,46; 6,84</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,63</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>6,1</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,92</t>
+          <t>6,29; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,08</t>
+          <t>5,55; 6,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 6,31</t>
+          <t>5,85; 6,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,86</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,06</t>
+          <t>2,87; 7,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,11</t>
+          <t>5,63; 6,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,1</t>
+          <t>5,61; 6,09</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,09</t>
+          <t>6,87; 7,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 7,33</t>
+          <t>6,07; 6,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,22</t>
+          <t>6,46; 6,66</t>
         </is>
       </c>
     </row>
